--- a/DAY24_Track1_2A202602407_DangVanThaiAnh.xlsx
+++ b/DAY24_Track1_2A202602407_DangVanThaiAnh.xlsx
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B15" s="111" t="inlineStr">
         <is>
-          <t>THU NGHIEM NHO: Co so cho thay du tien hoan von trong 18-24 thang voi NPV duong. Tuy nhien, kich ban xau can cat giam 30% chi phi co dinh neu churn vuot 7%/thang. Bat dau voi 1 truong/50 hoc sinh de do ti le roi bo that. Dieu kien mo rong: LTV/CAC &gt; 3 VA thang het tien &gt; 12 thang.</t>
+          <t>THỬ NGHIỆM NHỎ: NPV 24 tháng +472 triệu (IRR 49%/năm), LTV/CAC = 6,3. Cơ sở vững, kịch bản xấu vẫn có biên nhưng cần theo dõi churn. Quy mô: 1 trường · 100 học sinh · 4 tháng · vốn 1,5 tỷ. Nếu churn &gt; 7% trong 2 tháng liên tiếp: cắt 20% chi phí marketing, tạm dừng quảng cáo, cải thiện chất lượng. Điều kiện mở rộng: LTV/CAC &gt; 6, churn ≤ 4%, có ≥ 200 HS trong 6 tháng.</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B18" s="111" t="inlineStr">
         <is>
-          <t>Goi ket hop: 199.000 d/thang (50 bai) + 3.000 d/bai vuot han muc. Khach chap nhan vi: (1) tien loi hon gia su 500.000-1.000.000/thang; (2) tra ket qua ngay thay vi cho gia su cham; (3) co 50 bai mien phi/thang de thu. Ti le AI/doanh thu khach nhieu chi 21% - trong vung an toan &lt; 30%.</t>
+          <t>Gói kết hợp: 199.000 đ/tháng (50 bài) + 3.000 đ/bài vượt. Khách chấp nhận vì: (1) tiết kiệm 60-80% so với gia sư 500k-1tr/tháng; (2) chấm ngay thay vì đợi 1-2 ngày; (3) có 50 bài miễn phí/tháng để thử. Tỷ lệ AI/doanh thu khách dùng nhiều chỉ 21% - trong vùng an toàn &lt; 30%.</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B21" s="111" t="inlineStr">
         <is>
-          <t>Ty le roi bo (churn) la bien nguy hiem nhat. Neu tang tu 5% len 8%/thang, LTV giam 40%. Cach do: (1) theo doi so hoc sinh ngung su dung moi tuan; (2) phong van hoc sinh nghi ra hoc sau 2 thang dau; (3) khao sat muc do hai long moi thang. Nguoi phu trach: Product Manager.</t>
+          <t>Tỷ lệ rời bỏ (churn) là biến nguy hiểm nhất. Nếu tăng từ 4% lên 7%/tháng, LTV giảm ~43% và NPV có thể âm. Cách đo hằng tuần: (1) số HS ngưng dùng ÷ tổng HS đang dùng; (2) phỏng vấn HS nghỉ sau 2 tháng đầu; (3) khảo sát mức hài lòng tháng. Người phụ trách: Product Manager. Cập nhật vào bảng Ngày 23 mỗi tuần.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B24" s="111" t="inlineStr">
         <is>
-          <t>NEU ty le roi bo vuot 7% TRONG 2 thang lien tiep TREN 30 khach THI giam 20% chi phi marketing, tam dung quang cao Google, tap trung cai thien chat luong san pham. KHONG THI tiep tuc dau tu vao noi dung hoc tap de giu chan hoc sinh cu.</t>
+          <t>NẾU tỷ lệ rời bỏ &gt; 7% TRONG 2 tháng liên tiếp TRÊN 30 học sinh THÌ cắt 20% chi phí marketing, tạm dừng quảng cáo Google, tập trung cải thiện chất lượng sản phẩm và chương trình giữ chân. KHÔNG THÌ hạ giá gói cơ bản xuống dưới 199k hoặc giảm phí vượt dưới 3.000đ/bài (giữ ≥ giá sàn 2.229đ).</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B27" s="111" t="inlineStr">
         <is>
-          <t>Cac muc canh bao: (1) Bien loi nhuan &lt; 55% = NGUY; (2) Chi phi AI tang &gt; 20% = NGUY; (3) CAC vuot 2 trieu = NGUY; (4) Thang het tien &lt; 12 = CANH CANG CAT GIAM. Theo doi hang tuan boi Product Manager. Bang Ngay 23 se duoc cap nhat voi cac chi so nay.</t>
+          <t>Các mức cảnh báo đã ghi vào bảng Ngày 23: (1) Biên gộp &lt; 55% = NGUY; (2) Chi phí AI tăng &gt; 20% = NGUY; (3) CAC &gt; 1,2 triệu = NGUY; (4) Tiền mặt &lt; 12 tháng hoạt động = CẦN KẾ HOẠCH CẮT GIẢM. Theo dõi hằng tuần bởi Product Manager. Bảng Ngày 23 sẽ cập nhật 4 chỉ số này cùng với dòng tiền thực tế.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="C37" s="133" t="n">
-        <v>801</v>
+        <v>921</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="112">
@@ -3375,8 +3375,9 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="C41" s="133" t="n">
-        <v>1221</v>
+      <c r="C41" s="133">
+        <f>SUM(C37:C40)</f>
+        <v/>
       </c>
       <c r="G41" s="137">
         <f>IF(COUNT(C37:C41)&lt;5,"Chưa điền",IF(ABS(C41-SUM(C37:C40))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3397,7 +3398,7 @@
         </is>
       </c>
       <c r="C43" s="133" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="112">
@@ -3407,7 +3408,7 @@
         </is>
       </c>
       <c r="C44" s="133" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="112">
@@ -3426,8 +3427,9 @@
           <t>Tổng nợ phải trả</t>
         </is>
       </c>
-      <c r="C46" s="133" t="n">
-        <v>545</v>
+      <c r="C46" s="133">
+        <f>SUM(C43:C45)</f>
+        <v/>
       </c>
       <c r="G46" s="137">
         <f>IF(COUNT(C43:C46)&lt;4,"Chưa điền",IF(ABS(C46-SUM(C43:C45))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3467,8 +3469,9 @@
           <t>Tổng vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="C50" s="133" t="n">
-        <v>826</v>
+      <c r="C50" s="133">
+        <f>SUM(C48:C49)</f>
+        <v/>
       </c>
       <c r="G50" s="137">
         <f>IF(COUNT(C48:C50)&lt;3,"Chưa điền",IF(ABS(C50-SUM(C48:C49))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3481,8 +3484,9 @@
           <t>Tổng nợ phải trả + vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="C51" s="133" t="n">
-        <v>1371</v>
+      <c r="C51" s="133">
+        <f>C46+C50</f>
+        <v/>
       </c>
       <c r="G51" s="137">
         <f>IF(COUNT(C46,C50,C51)&lt;3,"Chưa điền",IF(ABS(C51-(C46+C50))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3572,7 +3576,7 @@
         </is>
       </c>
       <c r="C60" s="133" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="112">
@@ -3582,7 +3586,7 @@
         </is>
       </c>
       <c r="C61" s="133" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="112">
@@ -3591,8 +3595,9 @@
           <t>Dòng tiền từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="C62" s="133" t="n">
-        <v>11</v>
+      <c r="C62" s="133">
+        <f>SUM(C57:C61)</f>
+        <v/>
       </c>
       <c r="G62" s="137">
         <f>IF(COUNT(C57:C62)&lt;6,"Chưa điền",IF(ABS(C62-SUM(C57:C61))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3663,8 +3668,9 @@
           <t>Tiền tăng thêm trong kỳ</t>
         </is>
       </c>
-      <c r="C68" s="133" t="n">
-        <v>951</v>
+      <c r="C68" s="133">
+        <f>C62+C64+C67</f>
+        <v/>
       </c>
       <c r="G68" s="137">
         <f>IF(COUNT(C62,C64,C67,C68)&lt;4,"Chưa điền",IF(ABS(C68-(C62+C64+C67))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3687,8 +3693,9 @@
           <t>Tiền cuối kỳ</t>
         </is>
       </c>
-      <c r="C70" s="133" t="n">
-        <v>951</v>
+      <c r="C70" s="133">
+        <f>C68+C69</f>
+        <v/>
       </c>
       <c r="G70" s="137">
         <f>IF(COUNT(C68:C70)&lt;3,"Chưa điền",IF(ABS(C70-(C68+C69))&lt;0.01,"Đạt","Xem lại phép cộng"))</f>
@@ -3844,7 +3851,10 @@
           <t>Giá trị hiện tại của 36 tháng tiền thuê. Gợi ý: =PV(C85/12; C84; -C83). Dấu trừ trước C83 để kết quả là số dương; máy đặt tiếng Anh dùng dấu phẩy thay dấu chấm phẩy.</t>
         </is>
       </c>
-      <c r="C86" s="148" t="n"/>
+      <c r="C86" s="148">
+        <f>PV(C85/12,C84,-C83)</f>
+        <v/>
+      </c>
       <c r="G86" s="137">
         <f>IF(C86="","Chưa điền",IF(ABS(C86-PV(C85/12,C84,-C83))&lt;1,"Đạt","Xem lại"))</f>
         <v/>
@@ -3856,7 +3866,11 @@
           <t>Nên mua hay thuê? (chọn Mua hoặc Thuê trong danh sách)</t>
         </is>
       </c>
-      <c r="C87" s="149" t="n"/>
+      <c r="C87" s="149" t="inlineStr">
+        <is>
+          <t>Thuê</t>
+        </is>
+      </c>
       <c r="G87" s="137">
         <f>IF(C87="","Chưa điền",IF(C87=IF(PV(C85/12,C84,-C83)&lt;C82,"Thuê","Mua"),"Đạt","Xem lại"))</f>
         <v/>
@@ -3868,7 +3882,10 @@
           <t>Nếu chi phí vốn chỉ 8%/năm: giá trị hiện tại của tiền thuê (gợi ý: =PV(0,08/12; C84; -C83))</t>
         </is>
       </c>
-      <c r="C88" s="148" t="n"/>
+      <c r="C88" s="148">
+        <f>PV(0.08/12,C84,-C83)</f>
+        <v/>
+      </c>
       <c r="G88" s="137">
         <f>IF(C88="","Chưa điền",IF(ABS(C88-PV(0.08/12,C84,-C83))&lt;1,"Đạt","Xem lại"))</f>
         <v/>
@@ -3880,7 +3897,11 @@
           <t>Khi đó nên mua hay thuê?</t>
         </is>
       </c>
-      <c r="C89" s="149" t="n"/>
+      <c r="C89" s="149" t="inlineStr">
+        <is>
+          <t>Mua</t>
+        </is>
+      </c>
       <c r="G89" s="137">
         <f>IF(C89="","Chưa điền",IF(C89=IF(PV(0.08/12,C84,-C83)&lt;C82,"Thuê","Mua"),"Đạt","Xem lại"))</f>
         <v/>
@@ -5293,7 +5314,7 @@
         <v/>
       </c>
       <c r="C7" s="179" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D7" s="179">
         <f>C7*0.5</f>
@@ -5359,7 +5380,7 @@
         <v/>
       </c>
       <c r="C9" s="157" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D9" s="157">
         <f>C9*1.6</f>
@@ -5392,7 +5413,7 @@
         <v/>
       </c>
       <c r="C10" s="180" t="n">
-        <v>1500000</v>
+        <v>800000</v>
       </c>
       <c r="D10" s="180">
         <f>C10*1.5</f>
@@ -5425,7 +5446,7 @@
         <v/>
       </c>
       <c r="C11" s="180" t="n">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="D11" s="180">
         <f>C11</f>
@@ -5458,7 +5479,7 @@
         <v/>
       </c>
       <c r="C12" s="180" t="n">
-        <v>500000000</v>
+        <v>300000000</v>
       </c>
       <c r="D12" s="180">
         <f>C12</f>
@@ -5491,7 +5512,7 @@
         <v/>
       </c>
       <c r="C13" s="180" t="n">
-        <v>2000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="D13" s="180">
         <f>C13</f>
